--- a/REGLAS_COTIZADOR.xlsx
+++ b/REGLAS_COTIZADOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75A6AAAB-0C9E-44E5-90DB-292567C6D6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{5B7BBF7C-027C-4997-9ACE-77379B20A8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
